--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750339</v>
+        <v>123749918</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>58168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413475</v>
+        <v>413463</v>
       </c>
       <c r="R2" t="n">
-        <v>6249987</v>
+        <v>6250325</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750340</v>
+        <v>123750338</v>
       </c>
       <c r="B3" t="n">
-        <v>58165</v>
+        <v>57641</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123750271</v>
+        <v>123750339</v>
       </c>
       <c r="B4" t="n">
-        <v>57857</v>
+        <v>57643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413490</v>
+        <v>413475</v>
       </c>
       <c r="R4" t="n">
-        <v>6250092</v>
+        <v>6249987</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123749916</v>
+        <v>123748283</v>
       </c>
       <c r="B5" t="n">
-        <v>57857</v>
+        <v>57641</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,20 +1047,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,20 +1073,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Möllebäcken, Sk</t>
+          <t>Lanetorp, Lanetorp, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413463</v>
+        <v>413612</v>
       </c>
       <c r="R5" t="n">
-        <v>6250325</v>
+        <v>6250010</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1118,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123748283</v>
+        <v>123750340</v>
       </c>
       <c r="B6" t="n">
-        <v>57638</v>
+        <v>58168</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,20 +1168,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1193,21 +1194,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lanetorp, Lanetorp, Sk</t>
+          <t>Möllebäcken, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413612</v>
+        <v>413475</v>
       </c>
       <c r="R6" t="n">
-        <v>6250010</v>
+        <v>6249987</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123749918</v>
+        <v>123750271</v>
       </c>
       <c r="B7" t="n">
-        <v>58165</v>
+        <v>57860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,16 +1292,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413463</v>
+        <v>413490</v>
       </c>
       <c r="R7" t="n">
-        <v>6250325</v>
+        <v>6250092</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123750338</v>
+        <v>123749916</v>
       </c>
       <c r="B8" t="n">
-        <v>57638</v>
+        <v>57860</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,20 +1408,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413475</v>
+        <v>413463</v>
       </c>
       <c r="R8" t="n">
-        <v>6249987</v>
+        <v>6250325</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123749918</v>
       </c>
       <c r="B2" t="n">
-        <v>58168</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>123750338</v>
       </c>
       <c r="B3" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123750339</v>
+        <v>123750271</v>
       </c>
       <c r="B4" t="n">
-        <v>57643</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413475</v>
+        <v>413490</v>
       </c>
       <c r="R4" t="n">
-        <v>6249987</v>
+        <v>6250092</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123748283</v>
+        <v>123750340</v>
       </c>
       <c r="B5" t="n">
-        <v>57641</v>
+        <v>58169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,20 +1047,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,21 +1073,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lanetorp, Lanetorp, Sk</t>
+          <t>Möllebäcken, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413612</v>
+        <v>413475</v>
       </c>
       <c r="R5" t="n">
-        <v>6250010</v>
+        <v>6249987</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123750340</v>
+        <v>123748283</v>
       </c>
       <c r="B6" t="n">
-        <v>58168</v>
+        <v>57642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,20 +1167,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1194,20 +1193,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Möllebäcken, Sk</t>
+          <t>Lanetorp, Lanetorp, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413475</v>
+        <v>413612</v>
       </c>
       <c r="R6" t="n">
-        <v>6249987</v>
+        <v>6250010</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123750271</v>
+        <v>123750339</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,30 +1288,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413490</v>
+        <v>413475</v>
       </c>
       <c r="R7" t="n">
-        <v>6250092</v>
+        <v>6249987</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
         <v>123749916</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123749918</v>
+        <v>123750338</v>
       </c>
       <c r="B2" t="n">
-        <v>58169</v>
+        <v>57642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413463</v>
+        <v>413475</v>
       </c>
       <c r="R2" t="n">
-        <v>6250325</v>
+        <v>6249987</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750338</v>
+        <v>123749918</v>
       </c>
       <c r="B3" t="n">
-        <v>57642</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413475</v>
+        <v>413463</v>
       </c>
       <c r="R3" t="n">
-        <v>6249987</v>
+        <v>6250325</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123750271</v>
+        <v>123750340</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413490</v>
+        <v>413475</v>
       </c>
       <c r="R4" t="n">
-        <v>6250092</v>
+        <v>6249987</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123750340</v>
+        <v>123750271</v>
       </c>
       <c r="B5" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413475</v>
+        <v>413490</v>
       </c>
       <c r="R5" t="n">
-        <v>6249987</v>
+        <v>6250092</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750338</v>
+        <v>123750271</v>
       </c>
       <c r="B2" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413475</v>
+        <v>413490</v>
       </c>
       <c r="R2" t="n">
-        <v>6249987</v>
+        <v>6250092</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123749918</v>
+        <v>123750338</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413463</v>
+        <v>413475</v>
       </c>
       <c r="R3" t="n">
-        <v>6250325</v>
+        <v>6249987</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123750340</v>
+        <v>123748283</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>57642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,20 +927,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,20 +953,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Möllebäcken, Sk</t>
+          <t>Lanetorp, Lanetorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413475</v>
+        <v>413612</v>
       </c>
       <c r="R4" t="n">
-        <v>6249987</v>
+        <v>6250010</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123750271</v>
+        <v>123750339</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,30 +1048,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1083,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413490</v>
+        <v>413475</v>
       </c>
       <c r="R5" t="n">
-        <v>6250092</v>
+        <v>6249987</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1118,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123748283</v>
+        <v>123750340</v>
       </c>
       <c r="B6" t="n">
-        <v>57642</v>
+        <v>58169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,20 +1168,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1193,21 +1194,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lanetorp, Lanetorp, Sk</t>
+          <t>Möllebäcken, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413612</v>
+        <v>413475</v>
       </c>
       <c r="R6" t="n">
-        <v>6250010</v>
+        <v>6249987</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123750339</v>
+        <v>123749916</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,30 +1288,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413475</v>
+        <v>413463</v>
       </c>
       <c r="R7" t="n">
-        <v>6249987</v>
+        <v>6250325</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123749916</v>
+        <v>123749918</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750271</v>
+        <v>123749916</v>
       </c>
       <c r="B2" t="n">
         <v>57861</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413490</v>
+        <v>413463</v>
       </c>
       <c r="R2" t="n">
-        <v>6250092</v>
+        <v>6250325</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750338</v>
+        <v>123750339</v>
       </c>
       <c r="B3" t="n">
-        <v>57642</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123750339</v>
+        <v>123750271</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,30 +1048,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413475</v>
+        <v>413490</v>
       </c>
       <c r="R5" t="n">
-        <v>6249987</v>
+        <v>6250092</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123750340</v>
+        <v>123750338</v>
       </c>
       <c r="B6" t="n">
-        <v>58169</v>
+        <v>57642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,20 +1168,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123749916</v>
+        <v>123749918</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,16 +1292,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123749918</v>
+        <v>123750340</v>
       </c>
       <c r="B8" t="n">
         <v>58169</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413463</v>
+        <v>413475</v>
       </c>
       <c r="R8" t="n">
-        <v>6250325</v>
+        <v>6249987</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123749916</v>
+        <v>123750271</v>
       </c>
       <c r="B2" t="n">
         <v>57861</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413463</v>
+        <v>413490</v>
       </c>
       <c r="R2" t="n">
-        <v>6250325</v>
+        <v>6250092</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123748283</v>
+        <v>123749916</v>
       </c>
       <c r="B4" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,20 +927,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,21 +953,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lanetorp, Lanetorp, Sk</t>
+          <t>Möllebäcken, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413612</v>
+        <v>413463</v>
       </c>
       <c r="R4" t="n">
-        <v>6250010</v>
+        <v>6250325</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -999,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123750271</v>
+        <v>123750340</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1084,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413490</v>
+        <v>413475</v>
       </c>
       <c r="R5" t="n">
-        <v>6250092</v>
+        <v>6249987</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1276,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123749918</v>
+        <v>123748283</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>57642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,20 +1287,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,23 +1310,24 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Möllebäcken, Sk</t>
+          <t>Lanetorp, Lanetorp, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413463</v>
+        <v>413612</v>
       </c>
       <c r="R7" t="n">
-        <v>6250325</v>
+        <v>6250010</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123750340</v>
+        <v>123749918</v>
       </c>
       <c r="B8" t="n">
         <v>58169</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413475</v>
+        <v>413463</v>
       </c>
       <c r="R8" t="n">
-        <v>6249987</v>
+        <v>6250325</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750271</v>
+        <v>123749918</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413490</v>
+        <v>413463</v>
       </c>
       <c r="R2" t="n">
-        <v>6250092</v>
+        <v>6250325</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750339</v>
+        <v>123748283</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,42 +811,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Möllebäcken, Sk</t>
+          <t>Lanetorp, Lanetorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413475</v>
+        <v>413612</v>
       </c>
       <c r="R3" t="n">
-        <v>6249987</v>
+        <v>6250010</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1035,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123750340</v>
+        <v>123750339</v>
       </c>
       <c r="B5" t="n">
-        <v>58169</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,30 +1048,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1155,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123750338</v>
+        <v>123750340</v>
       </c>
       <c r="B6" t="n">
-        <v>57642</v>
+        <v>58169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,20 +1168,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1190,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1275,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123748283</v>
+        <v>123750271</v>
       </c>
       <c r="B7" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,20 +1288,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1313,21 +1314,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lanetorp, Lanetorp, Sk</t>
+          <t>Möllebäcken, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413612</v>
+        <v>413490</v>
       </c>
       <c r="R7" t="n">
-        <v>6250010</v>
+        <v>6250092</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123749918</v>
+        <v>123750338</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>57642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,20 +1408,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413463</v>
+        <v>413475</v>
       </c>
       <c r="R8" t="n">
-        <v>6250325</v>
+        <v>6249987</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750340</v>
+        <v>123750339</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123750339</v>
+        <v>123750340</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +927,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123748283</v>
+        <v>123750271</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,20 +1047,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,21 +1073,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lanetorp, Lanetorp, Sk</t>
+          <t>Möllebäcken, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413612</v>
+        <v>413490</v>
       </c>
       <c r="R5" t="n">
-        <v>6250010</v>
+        <v>6250092</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123749918</v>
+        <v>123748283</v>
       </c>
       <c r="B6" t="n">
-        <v>58191</v>
+        <v>57664</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,20 +1167,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1191,23 +1190,24 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Möllebäcken, Sk</t>
+          <t>Lanetorp, Lanetorp, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413463</v>
+        <v>413612</v>
       </c>
       <c r="R6" t="n">
-        <v>6250325</v>
+        <v>6250010</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123750271</v>
+        <v>123749918</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>58191</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413490</v>
+        <v>413463</v>
       </c>
       <c r="R8" t="n">
-        <v>6250092</v>
+        <v>6250325</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123749916</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,42 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750339</v>
+        <v>123750271</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413475</v>
+        <v>413490</v>
       </c>
       <c r="R3" t="n">
-        <v>6249987</v>
+        <v>6250092</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,32 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123750340</v>
+        <v>123748283</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,20 +938,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Möllebäcken, Sk</t>
+          <t>Lanetorp, Lanetorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413475</v>
+        <v>413612</v>
       </c>
       <c r="R4" t="n">
-        <v>6249987</v>
+        <v>6250010</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,32 +1021,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123750271</v>
+        <v>123750338</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1083,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413490</v>
+        <v>413475</v>
       </c>
       <c r="R5" t="n">
-        <v>6250092</v>
+        <v>6249987</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1118,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,15 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123748283</v>
+        <v>123750339</v>
       </c>
       <c r="B6" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,43 +1147,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lanetorp, Lanetorp, Sk</t>
+          <t>Möllebäcken, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413612</v>
+        <v>413475</v>
       </c>
       <c r="R6" t="n">
-        <v>6250010</v>
+        <v>6249987</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1239,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,32 +1251,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123750338</v>
+        <v>123749918</v>
       </c>
       <c r="B7" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,7 +1281,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1324,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413475</v>
+        <v>413463</v>
       </c>
       <c r="R7" t="n">
-        <v>6249987</v>
+        <v>6250325</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1359,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,15 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123749918</v>
+        <v>123750340</v>
       </c>
       <c r="B8" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1396,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1444,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413463</v>
+        <v>413475</v>
       </c>
       <c r="R8" t="n">
-        <v>6250325</v>
+        <v>6249987</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1479,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 8181-2025 artfynd.xlsx
+++ b/artfynd/A 8181-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123749916</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123750271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123748283</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123750338</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123750339</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123749918</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1478,8 +1513,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123750340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>